--- a/excel/distribuidora-aurelio-s-a-c_ruta_proxima_semana.xlsx
+++ b/excel/distribuidora-aurelio-s-a-c_ruta_proxima_semana.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C001748819</t>
+          <t>C004188118</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>21879123</t>
+          <t>23523687</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MUNAYCO ROJAS LUZ MARIA</t>
+          <t>NAHUI QUILCA LEONOR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,14 +543,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AV. ERNESTO VELIT 353 -Chincha Alta</t>
+          <t>PARADA MUNICIPAL Nº 124</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C001743077</t>
+          <t>C001670000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>47729136</t>
+          <t>48040744</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LOPEZ RAMOS FIORELLA ELISET</t>
+          <t>SOTELO DE LA CRUZ JESUS ALBERTO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -595,14 +595,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Av. Ernesto Velit 255</t>
+          <t>PARADA MUNICIPAL Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C004030169</t>
+          <t>C000960819</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>08329560</t>
+          <t>42912593</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CUYA ARANGO JESUS JOSE</t>
+          <t>CRISOSTOMO ALMEYDA YOLANDA MARIBEL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -647,14 +647,14 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AV. SANTOS NAGARO PUESTO 12</t>
+          <t>PARADA MUNICIPAL PSTO. 3A Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C001417899</t>
+          <t>C004183294</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74852080</t>
+          <t>21819484</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ALAY MENDOZA CARMEN MILAGROS</t>
+          <t>NAPA TORRES MARGARITA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,14 +699,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SANTOS NAGARO Ica-Chincha-Chincha Alta</t>
+          <t>Parada Municipal Pto 105</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C001378833</t>
+          <t>C004038734</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21804325</t>
+          <t>42150774</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HERNANDEZ DE ALMEYDA MARIA CRISTINA</t>
+          <t>CARDENAS SOLANO JOSE LUIS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -751,14 +751,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CL. MOISES FLORES NRO. 225 Ica-Chincha-Chincha Alta</t>
+          <t>CALLE SANTOS NAGARO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C004176772</t>
+          <t>C001628696</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10218154129</t>
+          <t>45292638</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PAUYAC LUYO MARIA LUISA</t>
+          <t>YARASCA BAUTISTA PAOLA LIZETH</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -803,14 +803,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CALLE ZOILA ATUNCAR DE ASIN Nº 136</t>
+          <t>PARADA MUNICIPAL Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -825,22 +825,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C004241129</t>
+          <t>C000956879</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21787707</t>
+          <t>10218398729</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CANDELA LUYO BENEDICTO ALVENERIO</t>
+          <t>GARAVITO FLORES MARIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -855,14 +855,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Calle Andrés Razuri 315</t>
+          <t>AV. MER DE ABASTOS P620 MZA. MAZAA590 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C004221110</t>
+          <t>C000956334</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10431730664</t>
+          <t>10217893475</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORTEZ TASAICO JULISSA MILAGROS</t>
+          <t>FELIX DE ROJAS MARIA AUGUSTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -907,14 +907,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Av. Santos Nagaro Mercado Ferial Pto 122</t>
+          <t>AV. MER DE ABASTOS P525 MZA. MAZAA590 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C004186523</t>
+          <t>C001347842</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15748639</t>
+          <t>40159226</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LUCIANO VEGA TORIBIO JUAN</t>
+          <t>LUNA OLIVARES BETTY CRISTINA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -959,14 +959,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AV. MARISCAL SUCRE S/N</t>
+          <t>MERCADO DE ABASTOS PSTO. 473 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -981,22 +981,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C001016326</t>
+          <t>C004042215</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10403892209</t>
+          <t>42286506</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PACHECO ORMENO VIVIANA CELESTE</t>
+          <t>CHICO APOLAYA ISRRAEL TIMOTEO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MERCADO FERIAL PTO NRO. 73 Ica-Chincha-Chincha Alta</t>
+          <t>MERCADO DE ABASTO 455</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C004030156</t>
+          <t>C000956292</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22299675</t>
+          <t>21861333</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CONISLLA CAYETANO MIRTHA GLADYS</t>
+          <t>CHACALIAZA DE LA CRUZ VICTOR NICOLAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CHINCHA</t>
+          <t>CAÑETE</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1063,14 +1063,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>MERCADO FERIAL PUESTO 27</t>
+          <t>AV. MERCADO DE ABASTOS MZA. 590 PSTO. 461 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1085,22 +1085,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C004093672</t>
+          <t>C001489757</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21810752</t>
+          <t>10218612615</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PACHAS TASAYCO JESUS</t>
+          <t>GARCIA PISCONTI YASENIA GETRUDIS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1115,14 +1115,14 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CALLE SUCRE S/N QUINTA CUADRA</t>
+          <t>MCDO. MERCADO DE ABASTOS PSTO. 258A Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C000961012</t>
+          <t>C000960655</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21820975</t>
+          <t>40382153</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CHING BENAVIDES HECTOR JAVIER</t>
+          <t>TATAJE TORRES JAVIER JESUS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>JR. SANTOS NAGARO MZA. 019 Ica-Chincha-Chincha Alta</t>
+          <t>MERCADO DE ABASTOS MZA. 023 PSTO. 479 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1189,22 +1189,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C004060558</t>
+          <t>C001499212</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48468713</t>
+          <t>10455992660</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>VALENCIA HUASASQUICHE CANDY STEFANIA</t>
+          <t>TORRES MARTINEZ ANGIE FABIOLA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1219,14 +1219,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>MERCADO FERIAL 177 CHINCHA ALTA</t>
+          <t>CL. CAQUETA NRO. 117 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1241,22 +1241,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C001715304</t>
+          <t>C001628870</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41112653</t>
+          <t>10218813769</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MENESES CHICO JULIO CESAR</t>
+          <t>ANDRADE DE LA CRUZ ALDO ANDRES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1271,14 +1271,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>MERCADO FERIAL Ica-Chincha-Chincha Alta</t>
+          <t>CL. ITALIA NRO. 372B Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C001429799</t>
+          <t>C001648238</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10400114493</t>
+          <t>10218437481</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>RONCEROS ALANYA YNGRID PAOLA</t>
+          <t>DEL RIO DE AGUIRRE JESUS MARIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1323,14 +1323,14 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PUESTO NRO. 162 URB. MERCADO FERIAL Ica-Chincha-Chincha Alta</t>
+          <t>CL. ITALIA NRO. 328 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1345,22 +1345,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C000961010</t>
+          <t>C001556504</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21819252</t>
+          <t>10703250241</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MUNAYCO GONZALES GEOVANNA ROSA</t>
+          <t>SALVATIERRA MACHUCA KARIN ELIANA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>JR. SANTOS NAGARO MZA. 020 Ica-Chincha-Chincha Alta</t>
+          <t>JR. PARADA MUNICIPAL  CHINCH NRO. 139 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1397,22 +1397,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C001531107</t>
+          <t>C004215672</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21829482</t>
+          <t>10780073018</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CARCAMO DE BELLIDO DOMENICA</t>
+          <t>CORDOVA HUAMAN KHENYI JHOEL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1427,14 +1427,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>MCDO. FERIAL Ica-Chincha-Chincha Alta</t>
+          <t>Calle Italia 240</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C001748822</t>
+          <t>C001370865</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73869499</t>
+          <t>21530294</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SANCHEZ DELGADO LITMAN YONEL</t>
+          <t>ESTEBAN CASAVILCA GLADYS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1479,14 +1479,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CL. ARICA Ica-Chincha-Chincha Alta</t>
+          <t>JR. SUCRE INT. 369 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1501,22 +1501,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C001506132</t>
+          <t>C001503283</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10218721287</t>
+          <t>40548513</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TASAYCO PACHAS MARIA YOVANNA</t>
+          <t>PACHAS BONIFACIO MARIA YSABEL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CL. MARISCAL SUCRE Ica-Chincha-Chincha Alta</t>
+          <t>CALLE CALLAO 326 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C004044565</t>
+          <t>C004029945</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21842647</t>
+          <t>21797224</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CHAVEZ VASQUEZ MARCIAL</t>
+          <t>BAUTISTA CHOQUE JUAN MARTIN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1583,14 +1583,14 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PARADA MUNICIPAL</t>
+          <t>CALLE EL CARMEN 235</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C004242574</t>
+          <t>C001660592</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41422964</t>
+          <t>21843325</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CANALES LIMA BRIGIDA CLARISA</t>
+          <t>OJEDA OJEDA MARTINA SABINA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1635,14 +1635,14 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Parada Municipal Chincha Alta</t>
+          <t>CALLE LIMA 200 COSTADO DEL BCP Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C001681573</t>
+          <t>C000961822</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10418182496</t>
+          <t>10218127270</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CERAZO LOPEZ MACARIA PAULA</t>
+          <t>DIAZ VILLAVICENCIO DELIA NORA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1687,14 +1687,14 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PROLOG ARICA NRO. 467 Ica-Chincha-Chincha Alta</t>
+          <t>JR. CAL COLON N112 NRO. 112 MZA. MAZAA029 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1709,22 +1709,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C001492131</t>
+          <t>C000956231</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21862119</t>
+          <t>10218125552</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>VALENTIN TUPAC MARLENE CRISTINA</t>
+          <t>SANCHEZ MOTTA GABY</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1739,14 +1739,14 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>JR. ARICA Ica-Chincha-Chincha Alta</t>
+          <t>CL. JIR COLON N199 NRO. 199 MZA. MAZAA350 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C004243894</t>
+          <t>C004244132</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10218631041</t>
+          <t>10422708281</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>VELIZ YATACO MARIO EDGARDO</t>
+          <t>PABLO ROMERO ADA LUZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Prolong. Arica 465</t>
+          <t>Jr. Colon 300</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1813,22 +1813,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C001443750</t>
+          <t>C001718496</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10218377110</t>
+          <t>21882002</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>YALLE RONDON DE PAUCAR JUANA MARIA</t>
+          <t>ALCA HERRERA ANGELA ELIZABETH</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1843,14 +1843,14 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CL. ANDRES RAZURI NRO. 433 Ica-Chincha-Chincha Alta</t>
+          <t>JR. SANTO DOMINGO Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C000962335</t>
+          <t>C001556397</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21867706</t>
+          <t>21840870</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TASAYCO GARCIA FLOR DE MARIA</t>
+          <t>PEREZ ELFONIO MOISES LUIS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1895,14 +1895,14 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PROLONG PEDRO MORENO 711 MZA. 10 -Chincha Alta</t>
+          <t>MERCADO MODELO Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1917,22 +1917,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C000956480</t>
+          <t>C001336373</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10218129329</t>
+          <t>21804847</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CASTILLA MIRANDA GUADALUPE</t>
+          <t>MERINO RIVERA DE LLANCARI ELEODORA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1947,14 +1947,14 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>AV. AVE MORENO PEDRO N688 NRO. 688 MZA. MAZAA100 URB. CHINCHA ALTA Ica-Chincha-Chincha Alta</t>
+          <t>MERCADO MODELO Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C004188107</t>
+          <t>C001687430</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41745504</t>
+          <t>21853611</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DE LA CRUZ GUERRA GUSTAVO ADOLFO</t>
+          <t>PATIÑO DE FERRER ROSA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1999,14 +1999,14 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SANTOS NAGARO Nº 102</t>
+          <t>CALLE LOS ANGELES126 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C001160765</t>
+          <t>C001731776</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45597799</t>
+          <t>73924637</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIAZ FLORES JUDITH MONICA</t>
+          <t>FRIAS SANCHEZ FAZIO FABRIZIO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2051,14 +2051,14 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SANTOS NAGARO Ica-Chincha-Chincha Alta</t>
+          <t>AV AVELARDO ALVA MAURTUA PASANDO LA RENIEC Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2073,22 +2073,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C001369944</t>
+          <t>C000960466</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10218471353</t>
+          <t>21871393</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FUENTES SALVADOR MARIA BLANCA ESTHER</t>
+          <t>LAURA CANCHARI OSWALDO ROQUE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>AV. PARAISO NRO. 14 Ica-Chincha-Sunampe</t>
+          <t>AV. BENAVIDES 899 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C001370197</t>
+          <t>C004069630</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21847092</t>
+          <t>41777374</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DE LA CRUZ DE GENTILLE DORIS GUILLERMINA</t>
+          <t>AVALOS LEVANO NANCY RUTH</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2150,19 +2150,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>AV. PARAISO NRO. 36 Ica-Chincha-Sunampe</t>
+          <t>AV. GROCIO PRADO 901 PUEBLO NUEVO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2177,22 +2177,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C004040873</t>
+          <t>C001481441</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21814114</t>
+          <t>10218560704</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ALVARADO TASSARA SANDRA NATALIA</t>
+          <t>RAMOS DE ROJAS YRMA ESTHER</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2202,19 +2202,19 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>AV. PARAISO 513</t>
+          <t>AV. BENAVIDES NRO. 1012 URB. AV BENAVIDES Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2229,22 +2229,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C001565197</t>
+          <t>C001288661</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20603693702</t>
+          <t>21813263</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AJL MULTISERVICIOS E.I.R.L.</t>
+          <t>SIGUAS CAMPOS DE ROMERO CANDELARIA VICTO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2254,19 +2254,19 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>AV. PARAISO NRO. 81 Ica-Chincha-Sunampe</t>
+          <t>JR. LIMA 241 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2281,22 +2281,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C004028248</t>
+          <t>C001158905</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>72717402</t>
+          <t>10218713217</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ROJAS ALMEYDA NAYDA LISBETH</t>
+          <t>DIAZ PEREZ ELIZABETH</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2306,19 +2306,19 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PASAJE SAN ANTONIO 101</t>
+          <t>AV. ARTEMIO MOLINA NRO. 1179 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C004008603</t>
+          <t>C004030149</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21886088</t>
+          <t>21872242</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SOTELO LOZA VICTOR MELCHOR</t>
+          <t>REYMUNDO PARIONA TEOFILA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2358,19 +2358,19 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Av. Primavera N° 105</t>
+          <t>JR. CHINCHA 221 ICA-CHINCHA-PUEBLO NUEVO</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C004039883</t>
+          <t>C004037620</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>21846211</t>
+          <t>70119340</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OCHOA PACHAS DE MENDOZA SOLEDAD</t>
+          <t>CAHUAPAS TORNERO MARILU NOELIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2410,19 +2410,19 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>CALLE JOSE OLAYA Mz C, Lote 6</t>
+          <t>CALLE FRANCISCO DE ZELA 462</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C004058896</t>
+          <t>C001374770</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>21852305</t>
+          <t>43717536</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CARPIO PACHAS LUISA NELLY</t>
+          <t>OCHOA HERRERA SOFIA VANESSA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2462,19 +2462,19 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>AV. PRIMAVERA 126 LOMO LARGO (COSTADO DE LA ANTENA)</t>
+          <t>CL. FRANCISCO DE ZELA 498 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C004036588</t>
+          <t>C001733927</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>21848239</t>
+          <t>75908775</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>LOPEZ CAYCHO CESAR GENARO</t>
+          <t>RODRIGUEZ PALOMINO LESLY JULISSA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>AV. PRIMAVERA 142 LOMO LARGO</t>
+          <t>CALLE CHINCHA 352 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C004030082</t>
+          <t>C000960458</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21869159</t>
+          <t>21871455</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>YATACO MUNAYCO YSABEL</t>
+          <t>VERA NUNEZ NORMA GREGORIA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>AV. PRIMAVERA 130</t>
+          <t>JR. CHINCHA 399 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C004030084</t>
+          <t>C001511045</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>72165108</t>
+          <t>21827328</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ATUNCAR FUENTES ELIZABETH PAOLA</t>
+          <t>AROTINCO DE DURAND SANTA BARBARA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2618,19 +2618,19 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>AV. PARAISO Mz C, Lote 21</t>
+          <t>AAHH MARIATEGUI / JR CHINCHA 497 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C004242613</t>
+          <t>C004050609</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>40975423</t>
+          <t>80632804</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AVALOS ALMEYDA GLADYS ROSA</t>
+          <t>FLORES CARDENAS JORGE LUIS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2670,19 +2670,19 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Av. Paraíso 108 Lomo Largo Sunampe</t>
+          <t>CALLE TUPAC AMARU 682 PUEBLO NUEVO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C001448652</t>
+          <t>C004065232</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10218462923</t>
+          <t>44308944</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ALMEYDA SALVADOR GRACIELA</t>
+          <t>AGUADO LOPEZ CHAI TIODOLINDA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2722,19 +2722,19 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CL. LAS MISIONERAS Ica-Chincha-Sunampe</t>
+          <t>AV. MICAELA BASTIDAS 541 SANTA ROSA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C001477089</t>
+          <t>C001488950</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>40265087</t>
+          <t>21840390</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>VIDALON NOA DELIA BERTHA</t>
+          <t>FLORES DE MADRID FELICITA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2774,19 +2774,19 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>URBANIZACION SAN ANTONIO NRO. 177 URB. FRENTE A AGENTE INTERBANK</t>
+          <t>AV. TUPAC AMARU 612 MZA. 210 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2801,22 +2801,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C001555062</t>
+          <t>C004178904</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10218485907</t>
+          <t>42866351</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CHAVEZ PRADA DE CANELO NELLY VICTORIA</t>
+          <t>BELLEZA QUISPE ROSARIO PATRICIA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2826,19 +2826,19 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>CL. LIMA NRO. 315 Ica-Chincha-Sunampe</t>
+          <t>CALLE MANCO INCA 409</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C004069734</t>
+          <t>C001378165</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>70401621</t>
+          <t>21871323</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>AMBROSIO MELO MONICA LISSET</t>
+          <t>ORTEGA TITO EDVINA LUISA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2878,19 +2878,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>URB. CASUARINAS Mz B Lote 4A SUNAMPE</t>
+          <t>AV. HERMANOS ANGULO 400 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C004178627</t>
+          <t>C001550279</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>45918959</t>
+          <t>21868849</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GARCIA ORELLANA ABEL FERNANDO</t>
+          <t>BALBUENA HUAMAN GUISELLA MARGOT</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2930,19 +2930,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>CALLE MONTERRICO S/N</t>
+          <t>CL. ANTONIO DE ZELA 352 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C001490980</t>
+          <t>C001379892</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>21847287</t>
+          <t>42416166</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ROJAS ATUNCAR VICTOR JAVIER</t>
+          <t>PAUCAR QUISPE RAQUEL MARIA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2982,19 +2982,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>AV. MONTERRICO NRO. 405 Ica-Chincha-Sunampe</t>
+          <t>AV. TUPAC AMARU 422 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C004179159</t>
+          <t>C001628395</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>47972869</t>
+          <t>21886624</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SILVA VILCHERREZ CARITO ELIZABETH</t>
+          <t>VILLA RAMOS ROXANA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3034,19 +3034,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>AV. EMANCIPACION 06</t>
+          <t>MERCADILLO SANTA ROSA PSTO. 36 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C001403893</t>
+          <t>C000962084</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>21846923</t>
+          <t>21836674</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SALCEDO FALCONI IDA PAULINA</t>
+          <t>MENDOZA DE CASIANO CRECENCIANA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>CALLE JOSE PARDO NRO. 205 Ica-Chincha-Sunampe</t>
+          <t>MERCADILLO SANTA ROSA NRO. 7 MZA. 038 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3113,22 +3113,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C000957338</t>
+          <t>C000962178</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>10218507480</t>
+          <t>21860563</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ATUNCAR CASTA EDA ROSA</t>
+          <t>MANSILLA SALVATIERRA OSCAR MOISES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3138,19 +3138,19 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>AV. EMANCIPACION NRO. 330 Ica-Chincha-Sunampe</t>
+          <t>MERCADILLO SANTA ROSA NRO. 31 MZA. 046 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>C004039877</t>
+          <t>C000961736</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>21873819</t>
+          <t>21858858</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>NAVARRO MARCELO ANITA</t>
+          <t>FLORES QUISPE FLORA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3190,19 +3190,19 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>CALLE EMAMCIPACION PASAJE CARMEN</t>
+          <t>MERCADILLO SANTA ROSA MZA. 045 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>C001499591</t>
+          <t>C001489129</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>45763766</t>
+          <t>21872800</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>AYLLON MANSILLA DIANA CAROLINA</t>
+          <t>RODRIGUEZ GUILLEN ANA ZORAIDA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3242,19 +3242,19 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>AV. EMAMCIPACION MZA. P LOTE. 2B Ica-Chincha-Sunampe</t>
+          <t>MERCADILLO SANTA ROSA PSTO. 16 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>C004044079</t>
+          <t>C000962609</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>80375332</t>
+          <t>21819155</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>VALLADARES ESPINOZA GLADYS MARILU</t>
+          <t>RODRIGUEZ GUILLEN DAYSI</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3294,19 +3294,19 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>AV. EMANCIPACION 500, INTERIOR 6</t>
+          <t>JR. SANTA ROSA S/N Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>C004030081</t>
+          <t>C004037332</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>75385718</t>
+          <t>21859405</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ATUNCAR ATUNCAR MARIA STEPHANY</t>
+          <t>SOTELO TASAYCO PEDRO ARTEMIO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3346,19 +3346,19 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PASO DE GOMEZ S/N</t>
+          <t>PN2 / MERCADILLO SANTA ROSA PUESTO 58</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3373,22 +3373,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>C000961008</t>
+          <t>C001070193</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>10218485419</t>
+          <t>21795065</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ALMEYDA MATIAS HUGO</t>
+          <t>MANSILLA SALVATIERRA CARMEN ROSA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3398,19 +3398,19 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>NRO. 304 URB. HUACA GRANDE Ica-Chincha-Sunampe</t>
+          <t>MCDO. MERCADILLO SANTA ROSA Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>C000959070</t>
+          <t>C004049669</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>21792605</t>
+          <t>45707125</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>YATACO CRISOSTOMO DE PACHAS MARIA ESTHER</t>
+          <t>HERRERA AGUIRRE CINDY</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3450,19 +3450,19 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>CL. 28 DE JULIO NRO. 302 Ica-Chincha-Sunampe</t>
+          <t>AV. SANTA ROSA 222 PUEBLO NUEVO</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3477,22 +3477,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>C001735278</t>
+          <t>C004167114</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>21874046</t>
+          <t>10410127160</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MELO PACHAS LILIANA EMILIA</t>
+          <t>MENESES VALENZUELA MARIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3502,19 +3502,19 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>AV. SIMON BOLIVAR NRO. 328 Ica-Chincha-Sunampe</t>
+          <t>JR. FRAY MARTIN 111</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3529,22 +3529,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>C000960700</t>
+          <t>C004028776</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>10218021617</t>
+          <t>47547497</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ALMEYDA DE SOTELO MARIA</t>
+          <t>CARHUAPUMA HURTADO DASLENNI JHANISSE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3554,19 +3554,19 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>MAL. PSJ SUCRE N107 NRO. 107 MZA. MAZAA017 Ica-Chincha-Sunampe</t>
+          <t>AVENIDA COLON 566 PUEBLO NUEVO</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-09-01 00:00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>C004196643</t>
+          <t>C004038251</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>21864994</t>
+          <t>40286160</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>QUISPE TIPISMANA YANINA MATILDE</t>
+          <t>MACHUCA PALOMINO EDITH ANICETA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3606,19 +3606,19 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Camino Real s/n Mina de Oro Sunampe</t>
+          <t>URB. OLIVA RAZETO Mz A, Lote 14</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>C004188825</t>
+          <t>C000956528</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>75517774</t>
+          <t>21808684</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>RAMOS JACOBO JHEISON DAVID</t>
+          <t>CABRERA CARBAJAL ROSA ELENA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3658,19 +3658,19 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Prolongación Rosario 534</t>
+          <t>AV. GARCILAZO DE LA VEGA 470 MZA. MANZANA030 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>C004028562</t>
+          <t>C001695040</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>21814129</t>
+          <t>10218873320</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>RAMIREZ GODOY ROSA</t>
+          <t>MORA AVALOS MARGARITA YOLANDA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3710,19 +3710,19 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CALLE ROSARIO 503 ICA-CHINCHA-CHINCHA ALTA</t>
+          <t>CL. ACEQUIA GRANDE NRO. 901 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>C001505835</t>
+          <t>C001405818</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>21803334</t>
+          <t>21803849</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FELIX DE GUERRA MARGARITA</t>
+          <t>PACHAS DE APOLAYA MARIA HILDA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3762,19 +3762,19 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>AV. ROSARIO 334 -Chincha Alta</t>
+          <t>PJE. LOS ROSALES  905 ACEQUIA GRANDE Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>C004167141</t>
+          <t>C001621504</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>73776511</t>
+          <t>21806597</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>VELAZCO NAPANGA KAREN EDITH</t>
+          <t>MURGUEYTIO MESIAS JULIA LAURIZA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3814,19 +3814,19 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>CALLE ROSARIO 312</t>
+          <t>PJE. LOS SAUCES 325 -Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>C004069847</t>
+          <t>C001653244</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>21813238</t>
+          <t>74890660</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>PATINO FLORES MARIA OFELIA</t>
+          <t>SOTELO RISPA MARGEORET GERALDINE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3866,19 +3866,19 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>CALLE ANTONIO DE ZELA 135 FRENTE A SEMAPACH</t>
+          <t>CL. CALLE MIRAFLORES NRO. 135 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>C001372573</t>
+          <t>C004008581</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>10218705559</t>
+          <t>45576812</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CHAVEZ HERRERA ROSANA JUVENCIA</t>
+          <t>MESIAS QUISPE GLORIA ELIZABETH</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3918,19 +3918,19 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>AV. PEDRO RONCEROS NRO. 104 INT. 01 Ica-Chincha-Chincha Alta</t>
+          <t>CALLE NICOLAS DE PIEROLA No 240</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>C001010092</t>
+          <t>C001480604</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>21871095</t>
+          <t>22309750</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>HUARACA ASTORAYME EDGARDO ABILIO</t>
+          <t>RUIZ FAJARDO ROSA ISABEL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3970,19 +3970,19 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>SANTOS NAGARO Ica-Chincha-Chincha Alta</t>
+          <t>CL. NICOLAS DE PIEROLA NRO. 176 MZA. 150 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>C004031739</t>
+          <t>C000962650</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>21828832</t>
+          <t>21854691</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ROMAN HUAMANI AGRIPINA GLADYS</t>
+          <t>TASAYCO ZAPATA ROSA PILAR</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4022,19 +4022,19 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>CALLE NICOLAS DE PIEROLA PUESTO 145</t>
+          <t>AV. SAN MARTIN NRO. 705 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4049,22 +4049,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>C004023374</t>
+          <t>C001562372</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>70878183</t>
+          <t>10458311965</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FLORES CHOQUE JULIO CESAR</t>
+          <t>MENDOZA LEVANO RAQUEL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4074,19 +4074,19 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>CALLE NICOLAS DE PIEROLA 253</t>
+          <t>NRO. 446 URB. BARRIO SAN MARTIN Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>C001523752</t>
+          <t>C001531420</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>77273299</t>
+          <t>41465146</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CCANTO HUARI JANIRA MILAGROS</t>
+          <t>DE LA CRUZ NOVA NORALI DEL CARMEN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>NICOLAS DE PIEROLA 202 SUCRE Ica-Chincha-Chincha Alta</t>
+          <t>PASAJE VICTORIA MZA. MK LOTE. 23 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>C001715312</t>
+          <t>C001454049</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>21819300</t>
+          <t>70149032</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HUAMAN HUAYLLANI MARGOT MARISOL</t>
+          <t>YATACO AYALA PAMELA LUCERO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4178,19 +4178,19 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>JR SUCRE 200 Ica-Chincha-Chincha Alta</t>
+          <t>AV. MINA DE ORO Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>C000959895</t>
+          <t>C001368585</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>10218012928</t>
+          <t>21849038</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SARAVIA SARAVIA JOSE MERCEDES</t>
+          <t>LEVANO AVALOS GLADYS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4230,19 +4230,19 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>AV. MER PARADITA MUNICIPAL P164 MZA. MAZAA190 Ica-Chincha-Chincha Alta</t>
+          <t>AV. MINA DE ORO NRO. 820 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>C000959538</t>
+          <t>C004049700</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>21815458</t>
+          <t>45449769</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CASTILLO CAMPOS ROCIO DEL PILAR</t>
+          <t>GUERRA CASTILLA MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4282,19 +4282,19 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>JR. SUCRE Ica-Chincha-Chincha Alta</t>
+          <t>CALLE FELIPE CHICO 190 SUNAMPE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C001723039</t>
+          <t>C001371658</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>21870090</t>
+          <t>21863662</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HILARION ACUNA ISAIAS ROMULO</t>
+          <t>AMORETTI SOTELO NORMA EVA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4334,19 +4334,19 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>CALLE SUCRE Ica-Chincha-Chincha Alta</t>
+          <t>AH DUBAI MINA DE ORO Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>C004049158</t>
+          <t>C001664100</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>73384831</t>
+          <t>41904913</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HILARION HUAYLLA JOSE LUIS</t>
+          <t>AVALOS CUBILLAS RUFINO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4386,19 +4386,19 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>JR. SUCRE CHINCHA</t>
+          <t>MINA DE ORO NRO. 100 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>C001371652</t>
+          <t>C001651237</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>21886769</t>
+          <t>74363339</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CARHUAPOMA HILARIO MARIVEL CRISTEL</t>
+          <t>TASAYCO VALDERRAMA GRISSEL IVON</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4438,19 +4438,19 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>MERCADO PARADA PUESTO 118</t>
+          <t>PJE. PASAJE APOLAYA NRO. 190 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4465,22 +4465,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>C001159230</t>
+          <t>C001413764</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>21862756</t>
+          <t>10476289071</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NAVARRO SARAVIA SILVIA ELENA</t>
+          <t>MARTINEZ MESIAS STEPHANIE MELISSA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4490,19 +4490,19 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Sunampe (Chincha)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>CHACHAPOYAS Ica-Chincha-Chincha Alta</t>
+          <t>AV. SAN MARTIN NRO. 134 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4517,22 +4517,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>C000959756</t>
+          <t>C001377639</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>10420254755</t>
+          <t>43099028</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CUEVAS PACHAS LUIS ALBERTO</t>
+          <t>MESIAS MORA AMELIA CATALINA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4547,14 +4547,14 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>AV. MER PARADITA MUNICIPAL I48 P INT. 48 MZA. MAZAA190 Ica-Chincha-Chincha Alta</t>
+          <t>CL. SANTO TOMAS NRO. 398 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>C004028744</t>
+          <t>C001481621</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>45278203</t>
+          <t>76957879</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ABURTO YATACO ALEX ROBERTO</t>
+          <t>GARCIA PASTOR JESUS ADEMIR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4599,14 +4599,14 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>PARADA MUNICIPAL PUESTO 63</t>
+          <t>AV. SAN MARTIN MZA. 021 LOTE. 3 Ica-Chincha-Sunampe</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>C004166807</t>
+          <t>C000957364</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>10468142282</t>
+          <t>10218790726</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CARBAJAL LLIUYA LUZ EVELYN</t>
+          <t>ALANYA CAHUANA MIRIAM</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>OTR. MERCADO LA PARADITA PUESTO 5</t>
+          <t>AV. OTR PAN SUR KM 199 N-728 NRO. 728 MZA. MANZANA39A URB. ANTES DE CHICO MUNAYCO</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4673,22 +4673,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>C001497344</t>
+          <t>C001398618</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>20601929334</t>
+          <t>21803933</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIAL DISTRIBUIDORA H &amp; C S.</t>
+          <t>MEDRANO UCEDA CONSUELO JULIA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4703,14 +4703,14 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>MERCADO PARADITA PUESTO 122/123 - Chincha Alta</t>
+          <t>AV. AMERICA N 236 NRO. 236 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>C001723032</t>
+          <t>C004182219</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>47430308</t>
+          <t>60753101</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>QUISPE PALOMINO EDDIE MERINIYES</t>
+          <t>OCHOA DIAZ KENNETH HANS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4755,14 +4755,14 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>PARADA MUNICIPAL Ica-Chincha-Chincha Alta</t>
+          <t>AV. AMERICA 208</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>C004007835</t>
+          <t>C001370356</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>73243847</t>
+          <t>21535927</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HUASASQUICHE SALAS SANTIAGO FELIPE</t>
+          <t>ZAPATA HERNANDEZ DE PALOMINO YRMA NELIDA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4807,14 +4807,14 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Calle Chachapoyas 117</t>
+          <t>SANTA ROSA DE LAS AMERICAS MZ A LOTE 5 - Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4829,22 +4829,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>C004036967</t>
+          <t>C000959392</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>42479278</t>
+          <t>10218245809</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PEVE PALOMINO YENIFER MARY</t>
+          <t>CHING BENAVIDES RAUL</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>CHACHALACAS PUESTO 126</t>
+          <t>JR. CAL MIGUEL GRAU N193 NRO. 193 MZA. MAZAA010 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4881,22 +4881,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>C000957976</t>
+          <t>C004054549</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>20367416191</t>
+          <t>42864200</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SANTA MARTHA S.R.LTDA.</t>
+          <t>GARCIA HERNANDEZ CATHY MARISELLA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>PARADA MUNICIPAL PUESTO 75</t>
+          <t>PROLONGACION SUCRE 816</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4933,22 +4933,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>C004064580</t>
+          <t>C001164813</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>21804585</t>
+          <t>10469938404</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>GONZALES GONZALES YSABEL APOLONIA</t>
+          <t>GOGIN GIL LAYZ ANTUHANE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4963,14 +4963,14 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Calle Sucre s/n</t>
+          <t>AV. GRAU NRO. 558 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>C004013473</t>
+          <t>C001742425</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>10218347962</t>
+          <t>10719831287</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>TASAYCO SARAVIA WALTER</t>
+          <t>CABRERA CARHUAPUMA DANIEL ANTONIO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5015,14 +5015,14 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Calle Mariscal Sucre No 324</t>
+          <t>CL. LIMA NRO. 596 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5037,22 +5037,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>C001532127</t>
+          <t>C001704335</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>47970087</t>
+          <t>10218072017</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>TASAYCO SITU ENZO GIUSEPPE</t>
+          <t>CASTILLO MARTINEZ DE YALAN LILIAN ADELIN</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5067,14 +5067,14 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>JR. SUCRE NRO. 324 Ica-Chincha-Chincha Alta</t>
+          <t>AV. FATIMA NRO. 236 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>C001492607</t>
+          <t>C004183477</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>21780449</t>
+          <t>21852257</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PACHAS HUAMAN NELLY</t>
+          <t>TASAYCO CASTILLA DE HUASASQUICHE MARIA V</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5119,14 +5119,14 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>JR. SUCRE Ica-Chincha-Chincha Alta</t>
+          <t>Av. Victoria 218</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>C001670529</t>
+          <t>C001693792</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>71196086</t>
+          <t>10402850901</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>TIPICIANO PENA DIANAKATTERINE</t>
+          <t>GALLO CASTILLA ROGELIO GUSTAVO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5171,14 +5171,14 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>FAUSTINO SANCHEZ CARRION URB. POR TACORA Ica-Chincha-Chincha Alta</t>
+          <t>CL. MIGUEL GRAU NRO. 479 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5193,22 +5193,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>C000956336</t>
+          <t>C000960787</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>21839068</t>
+          <t>10410923764</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SULLCAPUMA DE VARGAS CIRILA ROSA</t>
+          <t>LARENAS CASTILLA GUSTAVO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5218,19 +5218,19 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>CALLE ARICA 841 Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. MER MODELO P250 MZA. MAZAA370 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>C004039633</t>
+          <t>C001556310</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>42463178</t>
+          <t>43023491</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>PACHAS CASTILLA SINDIA RUTH</t>
+          <t>MUNAYCO VASQUEZ HAYDEE YANINA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5270,19 +5270,19 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>AV. ARICA 890 PUEBLO NUEVO</t>
+          <t>MERCADO MODELO Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>C004029936</t>
+          <t>C004014001</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5307,12 +5307,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>42605829</t>
+          <t>20996625</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ROMANI HUAMAN YOBANA AGUSTINA</t>
+          <t>MARTINEZ VARILLAS PATRICIA LILIANA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5322,19 +5322,19 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>AV. ARICA 702 PUEBLO NUEVO</t>
+          <t>MERCADO MODELO PUESTO 170 CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>C004187384</t>
+          <t>C001659080</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>21871415</t>
+          <t>10420645797</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>GUERRA QUISPE NOEMI</t>
+          <t>APOLAYA MARCOS DIANA EVELYN</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>UPIS LAS AMERICAS MZ A LT 15</t>
+          <t>CL. LUIS ALVA MAURTUA NRO. 317 INT. 2 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>C001383546</t>
+          <t>C004051480</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>21858281</t>
+          <t>43949735</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SULLCAPUMA OBAQUE DE PACHAS OTILIA CRIST</t>
+          <t>BONIFACIO DIAZ VENTURA MARIBEL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5426,19 +5426,19 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>AAHH LAS AMERICAS UNIDAS MZA. G LOTE. 7 Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. SAN MARTIN 136 CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>C001319603</t>
+          <t>C001216599</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>40224767</t>
+          <t>21794628</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>PALOMINO PENA ELIZABETH DEL ROSARIO</t>
+          <t>GRATTA DE ARBURUA ANGELITA MERCEDES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5478,19 +5478,19 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>AAHH LAS AMERICAS MZA. A LOTE. 1 Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. ALVA MAURTUA NRO. 680 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>C000961456</t>
+          <t>C001006107</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>21819173</t>
+          <t>21815165</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SUAREZ DE WONG VERONICA ISABEL</t>
+          <t>LEVANO MARCOS ANA MARIA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5530,19 +5530,19 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>PN2 / AAHH 28 DE JULIO MZA. C LOTE. 15 Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. LA FLORIDA  COSTADO HOSPITAL SAN JOSE Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>C001739301</t>
+          <t>C000960181</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>40302073</t>
+          <t>21790943</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SALVATIERRA MARTINEZ TANIA JANI</t>
+          <t>SALAZAR GONZALES MARITZA ELENA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5582,19 +5582,19 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>UPIS EL TREBOL  MZA. H LOTE. 23 Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. FLORIDA 310 MANZANA 390 - Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>C004216643</t>
+          <t>C004014312</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>48560098</t>
+          <t>41331524</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>TASAYCO HUANCAS ALEJANDRA VIVIANA</t>
+          <t>QUINTANA ISUIZA KELLY GERALDINE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5634,19 +5634,19 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>UPIS EL TREBOL MZ H LT22</t>
+          <t>Alva Maurtua Mz A Lt 5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5661,22 +5661,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>C001319591</t>
+          <t>C001548406</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>10218424401</t>
+          <t>21879015</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>LEVANO CHUQUISPUMA FABIANA SIMONA</t>
+          <t>MOSCAYZA ARTEAGA FANNY</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5686,19 +5686,19 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>AV. V A BELAUNDE NRO. 1088 URB. AV VICTOR ANDRES BELAUNDE Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. GERARDO SOTELO MZA. T LOTE. 9 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>C004188826</t>
+          <t>C004060584</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>21871112</t>
+          <t>21804090</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>VELASQUEZ DIANDERAS CELIA SOBEIDA</t>
+          <t>SEBASTIAN CABALLERO JUANA NELLY</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5738,19 +5738,19 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Av. Víctor Andrés Belaunde 965</t>
+          <t>AV. GERARDO SOTELO Lote 10 CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>C001541087</t>
+          <t>C004176969</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>09682077</t>
+          <t>48310476</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>VENTO INGA MARIA ISABEL</t>
+          <t>HUARIPAUCAR LIFONZO MARIA LUISA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5790,19 +5790,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>JR. LIMA 447 Ica-Chincha-Pueblo Nuevo</t>
+          <t>PROLONG. ALVA MAURTUA 190</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>C004178433</t>
+          <t>C001375507</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>21884825</t>
+          <t>10217996517</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PARI DE LAURA ROSA EUFRACIA</t>
+          <t>GONZALES HUAMANI LEONOR AURELIA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5842,19 +5842,19 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>AV. SAN MARTIN 1069</t>
+          <t>CL. CHAVALINA NRO. 130 INT. 01 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>C004177211</t>
+          <t>C001370891</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>21856079</t>
+          <t>21812115</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MARTINEZ FELIPA SONIA ANGELA</t>
+          <t>AGURTO INOQUIO JUANA INES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5894,19 +5894,19 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>AV. SAN MARTIN 509</t>
+          <t>PROLONG COLON NRO. 706 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>C000957454</t>
+          <t>C001552713</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>21842974</t>
+          <t>21808446</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>RAMIREZ QUISPE ALEJANDRO FELIX</t>
+          <t>CESPEDES ALMEYDA MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5946,19 +5946,19 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO MZA. 310 PSTO. P-4 Ica-Chincha-Pueblo Nuevo</t>
+          <t>CALLE SANTO DOMINGO 621 INT. 7 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>C004043511</t>
+          <t>C001738166</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>75473798</t>
+          <t>75480015</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>FLORES YAURI FABIO DAVID</t>
+          <t>LOBATON MARCELO MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5998,19 +5998,19 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO PUESTO 10- SECCIÓN ABARROTES</t>
+          <t>PLZ. PROLONG SANTO DOMINGO NRO. 621 INT. 6 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>C004032625</t>
+          <t>C001738817</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>21876409</t>
+          <t>45912779</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ASTORAYME MARCA YODINA EMPERATRIZ</t>
+          <t>MAGALLANES ALVAREZ SCHEYLA ELOISA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6050,19 +6050,19 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>AV. VICTOR ANDRES BELAUNDE PUESTO 35</t>
+          <t>CALLE COLON 594 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>C001288644</t>
+          <t>C001216596</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>21828401</t>
+          <t>23524279</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HUAMANI ONTIVERO RINA YSABEL</t>
+          <t>DEL RIO DE SALVATIERRA LUZMILA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6102,19 +6102,19 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO PUESTO 49 SECCIÓN ABARROTES</t>
+          <t>AV. ANDRES AVELINO CACERES 148 POR EL COLISEO - Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>C001087257</t>
+          <t>C004048135</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>21838858</t>
+          <t>62021171</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>YATACO LEVANO ROSALVINA</t>
+          <t>PADILLA PINO ALYSON LORENA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6154,19 +6154,19 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO Ica-Chincha-Pueblo Nuevo</t>
+          <t>PASAJE GARAY 198 CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>C000961029</t>
+          <t>C001495873</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>23532297</t>
+          <t>21782651</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ACHARTE CULLANCO MERY DORIS</t>
+          <t>CHACALIAZA VELIZ EDITH PIEDAD</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6206,19 +6206,19 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO MZA. 024 PSTO. 32 Ica-Chincha-Pueblo Nuevo</t>
+          <t>PASAJE OLAYA NRO. 620 INT. 6 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>C001725216</t>
+          <t>C000961864</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>75078611</t>
+          <t>21863612</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>MEZA SALAZAR BRANDON YOEL</t>
+          <t>HUAMAN AVALOS ELIZABETH ROSARIO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6258,19 +6258,19 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO PUESTO 15 SECCIÓN ABARROTES</t>
+          <t>AV. LUIS MASSARO 793 MZA. MANZANA034  Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6285,22 +6285,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>C004029968</t>
+          <t>C001565925</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>73823704</t>
+          <t>10760415591</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>JIMENEZ PEVE LUZ MARIA</t>
+          <t>PASACHE CHACALIAZA CAROLIN DEYANIRA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6310,19 +6310,19 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO PUESTO 2 SECCIÓN ABARROTES</t>
+          <t>AV. PILPA NRO. 811 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>C004172212</t>
+          <t>C001687429</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>41573933</t>
+          <t>41223811</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>MORALES ROMERO SILVIA ROSARIO</t>
+          <t>TASAYCO DE LA CRUZ SARA MARIANELLA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6362,19 +6362,19 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>AV. VICTOR ANDRES BELAUNDE - MERCADO P. NUEVO</t>
+          <t>AV. LUIS MASSARO 819 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>C001470525</t>
+          <t>C000959225</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>42382952</t>
+          <t>21868561</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>VILCHEZ ELIAS VANESSA DEL ROSARIO</t>
+          <t>ORTIZ MARCOS DE PACHAS MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6414,19 +6414,19 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO PUESTO 9 SECCIÓN TUBÉRCULOS</t>
+          <t>AV. VICTORIA 311 POR COLEGIO COOPERATIVO Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>C001737256</t>
+          <t>C004036014</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>42612073</t>
+          <t>21812546</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>RAMOS ROMERO MARILUZ LILIANA</t>
+          <t>QUISPE GUERRA MARIA DEL PILAR</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6466,19 +6466,19 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. VICTORIA 265 CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>C001551841</t>
+          <t>C004039631</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>73578718</t>
+          <t>21874798</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>TASAYCO MAGALLANES YEISY MEDALIT</t>
+          <t>LOZANO CARBAJAL VDA DE MEDINA GLORIA NIL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6518,19 +6518,19 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO PUESTO 21 - SECCIÓN AVES , AVENIDA 13 DE OCTUBRE - Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. PILPA 751</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>C004011479</t>
+          <t>C001714400</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>40670309</t>
+          <t>47979929</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>MAGUINA LOPEZ SHIRLEY DESSIREDT</t>
+          <t>BONIFACIO CHAVEZ JAHAIRA ROSITA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6570,19 +6570,19 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Av. 13 de Octubre s/n ICA-CHINCHA-PUEBLO NUEVO</t>
+          <t>CALLE JUNIN NRO. 501 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6597,22 +6597,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>C001454048</t>
+          <t>C001130302</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>45450787</t>
+          <t>10218131315</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>VILCAPUMA YAURI MARLENE FIORELLA</t>
+          <t>RONCEROS FIGUEROA CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6622,19 +6622,19 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO Ica-Chincha-Pueblo Nuevo</t>
+          <t>CL. SAN JOSE NRO. 198 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>C004064573</t>
+          <t>C004183666</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>44835712</t>
+          <t>21815460</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>JAIME AMORETTI MAURA TRINIDAD</t>
+          <t>CRISOSTOMO FELIX GLORIA LILY</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6674,19 +6674,19 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Av. 13 de Octubre nº 743</t>
+          <t>Pasaje Marcela 807-30</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-09-03 00:00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>C000957551</t>
+          <t>C000956193</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>10218556758</t>
+          <t>10218014122</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>RAMIREZ DE MATTA ESPERANZA</t>
+          <t>VELIZ VALENZUELA SARELA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6726,19 +6726,19 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>AV. AVE PRIMAVERA N596 NRO. 596 MZA. MAZAA130 Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. AVE BOM BOM CORONADO N787 NRO. 787 MZA. MAZAA18C URB. CHINCHA ALTA Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>C004243884</t>
+          <t>C001559793</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>44519213</t>
+          <t>47144070</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>YOVERA MAGALLANES VERONICA</t>
+          <t>ZEVALLOS OCHOA MARIA ANDREA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6778,19 +6778,19 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Av. San Martin 200 Huayabo cholo</t>
+          <t>CALLE GERARDO SOTELO 299 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>C001718654</t>
+          <t>C001675821</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>21812849</t>
+          <t>21878498</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DE LA CRUZ NOVA WALTER WILLIAM</t>
+          <t>CCAPA CRUZ DE PACHAS SANDRA MARIBEL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6830,19 +6830,19 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>TUPAC AMARU NRO. 750 URB. ESPALDA HOTEL IMPERIO</t>
+          <t>AV GROCIO PRADO 140 - Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>C001367411</t>
+          <t>C004023217</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>45655545</t>
+          <t>77815250</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>NUNEZ SOTELO PAMELA LUCILA</t>
+          <t>VELA PISCO MAGNO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6882,19 +6882,19 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>PROLONG RAZURI NRO. 515 URB. POR CORTESA - Sunampe</t>
+          <t>AV. PROGRESO 175 ICA-CHINCHA-CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>C001468365</t>
+          <t>C004063319</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>48382371</t>
+          <t>46578852</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>VASQUEZ CARDENAS MARIA JIMENA</t>
+          <t>ANGEL MENDOZA ANGELA GRACIELA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6934,19 +6934,19 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>CALLE SANTA ROSA  719 INT. 03 Chincha Alta</t>
+          <t>Upis Aurora Castilla Mz D Lt 14</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>C001215547</t>
+          <t>C004193400</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>21828929</t>
+          <t>42704404</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>PAUCAR BALDEON LUIS RAUL</t>
+          <t>RAYGAL MONTALVO YULI MILAGROS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6986,19 +6986,19 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>PASAJE ACUARIO S/N - Sunampe</t>
+          <t>Upis Aurora Castilla Lévano  Mz A Lote 10</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>C000960175</t>
+          <t>C004159780</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>21784591</t>
+          <t>77144063</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ESPINOZA PACHAS DE APOLAYA IRENE DISNARD</t>
+          <t>VALENCIA MARTINEZ JEAN PIERRE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7038,19 +7038,19 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>CALLE TUPAC AMARU  417 LOTE. 9 GRIFO SINDICATO -Chincha Alta</t>
+          <t>PSJE. SALOMON FRENTE COLEGIO INICIAL CHAVALINA</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7065,22 +7065,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>C004237867</t>
+          <t>C001729366</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>20615517420</t>
+          <t>21864311</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>MINI MARKET GREEN POINT E.I.R.L.</t>
+          <t>MAGALLANES PACHAS ROBERT EMERSON</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7095,14 +7095,14 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CAR. PANAMERICANA SUR KL. 199</t>
+          <t>AV. CHAVALINA 280 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>C001493327</t>
+          <t>C001370888</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>21877465</t>
+          <t>21863400</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>OLIVERO TORRES GLORIA YSABEL</t>
+          <t>MENESES MAGALLANES JOVANA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7147,14 +7147,14 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>MERCADO DE ABASTOS Ica-Chincha-Chincha Alta</t>
+          <t>PROLONG COLON 785 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>C001398601</t>
+          <t>C001403118</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>21798100</t>
+          <t>41680405</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>MARCOS LEVANO JOSE MIGUEL</t>
+          <t>TAPIA YAMOCA ROSA YSABEL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7199,14 +7199,14 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO DE ABASTOS Ica-Chincha-Chincha Alta</t>
+          <t>BARRIO CHAVALINA 371 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>C001509477</t>
+          <t>C001571354</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>10217908766</t>
+          <t>21869871</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>VALENTIN TUPAC ANASTACIO LIBORIO</t>
+          <t>NOLAZCO HUAYTA YSABEL CRISTINA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -7251,14 +7251,14 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>URB. MERCADO DE ABASTOS Ica-Chincha-Chincha Alta</t>
+          <t>AV. CENTENARIO MZA. 8 LOTE 1 - Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>C004022981</t>
+          <t>C004033225</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>46196516</t>
+          <t>80042981</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>APOLAYA DE LA CRUZ WALTER ALEXIS</t>
+          <t>ENRIQUEZ DE LA CRUZ CARMEN ROSA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7303,14 +7303,14 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>MERCADO DE ABASTOS PUSTO 233-234</t>
+          <t>JR. INCA ROCA S/N CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7325,22 +7325,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>C001553069</t>
+          <t>C001748920</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>10218137763</t>
+          <t>74486009</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>PACHAS CERVANTES NANCY GLADYS</t>
+          <t>HERRERA QUISPE YAHAIRA LISETH</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>AV. OSCAR R BENAVIDES NRO. 350 INT. 49 URB. MERCADO DE ABASTOS Ica-Chincha-Chincha Alta</t>
+          <t>UPIS SAN AGUSTIN MZA. B1 LOTE. 24 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7377,22 +7377,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>C004189307</t>
+          <t>C000956246</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>10426841695</t>
+          <t>21856545</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SARAVIA ARROYO MARIA DEL ROSARIO</t>
+          <t>PEREZ MACHUCA SILVIA BELEN</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>OTR. Mercado de Abastos s/n puesto 449-450</t>
+          <t>UPIS SAN AGUSTIN MB1 L27 MZA. MANZANA350 LOTE. 27</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7429,22 +7429,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>C001642509</t>
+          <t>C001362735</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>10218153181</t>
+          <t>21858573</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>TALLA DE LA CRUZ ESPERANZA</t>
+          <t>ENRRIQUEZ CARCAMO LUZ ADELVINA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7459,14 +7459,14 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>AV. OSCAR R BENAVIDES INT. 282 URB. MERCADO DE ABASTOS Ica-Chincha-Chincha Alta</t>
+          <t>UPIS SAN AGUSTIN MZA. H LOTE. 7 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7481,22 +7481,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>C001488850</t>
+          <t>C001526321</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>10217990331</t>
+          <t>77472574</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>AVALOS QUISPE LUIS ALBERTO</t>
+          <t>QUIJAITE DEL RIO ANA MILAGROS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7511,14 +7511,14 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>MCDO. DE ABASTOS NRO. 105 INT. 106 Ica-Chincha-Chincha Alta</t>
+          <t>UPIS SAN AGUSTIN MZA. V LOTE. 4 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>C004044562</t>
+          <t>C004065709</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>43144358</t>
+          <t>60887139</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CAPCHA CONDORI JOHN EDMERT</t>
+          <t>RODRIGUEZ CLEMENTE LEONEL EDMILSON</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -7563,14 +7563,14 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>MERCADO DE ABASTOS PSTO 512</t>
+          <t>UPIS SAN AGUSTIN Mz V Lote 01 CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7585,22 +7585,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>C001421817</t>
+          <t>C004214398</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>10217871650</t>
+          <t>44236376</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>GUERRA DE JACOBO AIDA</t>
+          <t>QUISPE MUCHA VICENTA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7615,14 +7615,14 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>CL. ITALIA PSTO 584-585 INT. 586 URB. MERCADO ABASTOS Ica-Chincha-Chincha Alta</t>
+          <t>Upis San Agustín Mz 1 Lote 16</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>C001541187</t>
+          <t>C004183669</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>41814584</t>
+          <t>23270717</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CRISOSTOMO MARTINEZ YLANCARLOS</t>
+          <t>QUISPE CHANCHA JORGE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7667,14 +7667,14 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>MERCADO DE ABASTOS PSTO. 258 Ica-Chincha-Chincha Alta</t>
+          <t>Upis San Agustín Mz 1 Lote 19</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7689,22 +7689,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>C004001813</t>
+          <t>C001666047</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>10217880144</t>
+          <t>75490737</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SOTELO ALMEYDA MARIO RICARDO</t>
+          <t>ENRIQUE HUAMAN CINTHIA MARIA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7719,14 +7719,14 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Mercado Abasto</t>
+          <t>UPIS SAN AGUSTIN LOTE. 16 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7741,22 +7741,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>C000960113</t>
+          <t>C001511661</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>10218801400</t>
+          <t>21865305</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>CAYLLAHUA CORDOVA ALBERTO</t>
+          <t>TENORIO PARIONA DE PUMA SANDY GRACIELA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7771,14 +7771,14 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>AV. MER DE ABASTOS P19 MZA. MAZAA230 Ica-Chincha-Chincha Alta</t>
+          <t>UPIS SAN AGUSTIN MZA. U LOTE. 28 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7793,22 +7793,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>C001530995</t>
+          <t>C004008216</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>10282927981</t>
+          <t>21878830</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HUAMAN CAYLLAHUA JHONY FORTUNATO</t>
+          <t>MARTINEZ SALVATIERRA GLORIA HILDA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>PJE. OESTE NRO. PSTO INT. 28 URB. MERCADO ABASTOS Ica-Chincha-Chincha Alta</t>
+          <t>UPIS SAN AGUSTIN MAZ.A1 LOTE 33</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>C001572565</t>
+          <t>C001508654</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>10439046177</t>
+          <t>48577684</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MARTINEZ APOLAYA JESUS ALEJANDRO</t>
+          <t>CHAVEZ RONDON GABRIELA LUZ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7875,14 +7875,14 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>CL. CHACHAPOYA NRO. 254 INT. C Ica-Chincha-Chincha Alta</t>
+          <t>UPIS SAN AGUSTIN MZA. Q LOTE. 6 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7897,22 +7897,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>C004013469</t>
+          <t>C004008205</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>10218429829</t>
+          <t>23524036</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>GONZALES DE ROMANI SANTA SATURNINA</t>
+          <t>FLORES DE SALVATIERRA JESUSA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -7927,14 +7927,14 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Calle Chachapoyas N° 281</t>
+          <t>UPIS SAN AGUSTIN MAZ. F LOTE 3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7949,22 +7949,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>C001160038</t>
+          <t>C001507939</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>10412783757</t>
+          <t>21858250</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DURAN HUARANCA SONIA ELENA</t>
+          <t>DAVALOS MUNARRIZ ELMARIA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7979,14 +7979,14 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>PUESTO NRO. 85 URB. MERCADO FERIAL Ica-Chincha-Chincha Alta</t>
+          <t>UPIS SAN LUIS INT. 7 MZA. H Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>C001332461</t>
+          <t>C004008213</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>10432431598</t>
+          <t>23533455</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>MENESES GUZMAN JAIRO RAFAEL</t>
+          <t>DIAZ MONDALGO FLORISA TOLENTINA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>AV. MERCADO FERIAL ARICA NRO. 88 Ica-Chincha-Chincha Alta</t>
+          <t>UPIS SAN AGUSTIN MAZ.I LOTE 22</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>C004188124</t>
+          <t>C001508647</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>45963817</t>
+          <t>21885050</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>VERGARA MAGALLANES CAROLINA MILAGROS</t>
+          <t>HUAYLLANI TAIPE NELFA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8083,14 +8083,14 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>CHACHAPOYAS Nº 301</t>
+          <t>UPIS SAN AGUSTIN MZA. K LOTE. 40 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>C004184996</t>
+          <t>C004007842</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>46397294</t>
+          <t>21784294</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>AVALOS ORTIZ MARIA DEL ROSARIO</t>
+          <t>CAQUIAMARCA GODOY SILVERIA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8130,19 +8130,19 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>ACEQUIA GRANDE 861-01</t>
+          <t>Upis San Agustin Mz. D Lt. 25</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>C004218449</t>
+          <t>C004189117</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>71882005</t>
+          <t>41374467</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>PALOMINO LEVANO MELISA PAOLA</t>
+          <t>ORMEÑO PEÑALOZA SANDY LISSET</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>AV. SAN IDELFONSO S/N</t>
+          <t>AA.HH Villa Sol Mz F Lote 13 José Olaya</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -8209,22 +8209,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>C001532687</t>
+          <t>C000960753</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>21793069</t>
+          <t>10218432218</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>TORRES DE MONDALGO JESUS MARIA</t>
+          <t>CARRION DE SALVATIERRA REYMUNDA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8234,19 +8234,19 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>PJE. SAN MARTIN NRO. 351 Ica-Chincha-Sunampe</t>
+          <t>AV. GROCIO PRADO NRO. 332 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-09-04 00:00:00</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>C001709601</t>
+          <t>C004008541</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>21790988</t>
+          <t>21876118</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FUENTES CAVERO DE VASQUEZ MARIA YSABEL</t>
+          <t>VELASCO SANCHEZ JUANITA JUSTINA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8286,19 +8286,19 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Sunampe (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>AV. GARCILAZO DE LA VEGA 223 Ica-Chincha-Sunampe</t>
+          <t>Jr. Cahuide Mz K, Lt 14 ICA-CHINCHA-PUEBLO NUEVO</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -8313,22 +8313,22 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>C001728530</t>
+          <t>C001433290</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>48555176</t>
+          <t>10409754282</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>PAUCAR TOVAR YHANDIRA LILIANA</t>
+          <t>BELLEZA CARPIO ANGELA ELIZABETH</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -8338,19 +8338,19 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Chincha Alta (Chincha)</t>
+          <t>Pueblo Nuevo (Chincha)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>AV 13 DE OCTUBRE 124 Ica-Chincha-Pueblo Nuevo</t>
+          <t>MZA. C LOTE. 02 URB. URB OLIVA RAZZETO Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>C004187824</t>
+          <t>C004016284</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8375,12 +8375,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>21866687</t>
+          <t>21794656</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SOTELO QUISPE JESSICA GLORIA</t>
+          <t>QUINCHO QUINCHO MELCHORA FELICIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8395,14 +8395,14 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>JR. 23 DE MAYO Nº 672</t>
+          <t>Urb. Oscar R. Benavides - Rosedal Mz D Lt 10</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>C004192320</t>
+          <t>C001733929</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>41263495</t>
+          <t>48164409</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SOTELO QUISPE MARIBEL ALMENDRA</t>
+          <t>SALVATIERRA MOTTA YAMELI MILAGROS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -8447,14 +8447,14 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Av. 23 de Mayo 672</t>
+          <t>URB. OLIVA RAZZETO 1 MZA. D LOTE. 06 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>C004094381</t>
+          <t>C001086594</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>71440776</t>
+          <t>21844364</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>TORRES RIVAS DAYANA KAREN</t>
+          <t>RAMOS CAHUANA SONIA ISABEL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8499,14 +8499,14 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>AV. VICTOR ANDRES BELAUNDE 318</t>
+          <t>AAHH MICAELA BASTIDA MZA. E LOTE. 7 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>C001721221</t>
+          <t>C004097166</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>46119140</t>
+          <t>07070448</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>IDONE YACTAYO ZAIRA VERONICA</t>
+          <t>PALOMINO OBIAGA ESTHER</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8551,14 +8551,14 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>AV. SAN MARTIN 418 Ica-Chincha-Pueblo Nuevo</t>
+          <t>JR. CUZCO Mz E Lote 4</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>C004221528</t>
+          <t>C001733931</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>76033971</t>
+          <t>44817388</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>ANTON ONCEVAY ERICKA EDUARDA</t>
+          <t>MAGALLANES MUNAREZ ELIZABET VALENTINA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8603,14 +8603,14 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Av. San Martin 501</t>
+          <t>AAHH MICAELA BASTIDAS MZA. G LOTE. 10A Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>C001490615</t>
+          <t>C004185405</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8635,12 +8635,12 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>44350201</t>
+          <t>62723782</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>VARA PANCA EVELYN SUSANA</t>
+          <t>MARTINEZ MACHUCA KENIA ELIZABETH</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8655,14 +8655,14 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>AV. SAN MARTIN 700 Ica-Chincha-Pueblo Nuevo</t>
+          <t>AA.HH MICAELA BASTIDAS MZ G LT 12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>C004038716</t>
+          <t>C000957808</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>72017464</t>
+          <t>21829370</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>JUSCAMAITA FLORES MILENNE MIRIAM</t>
+          <t>NAPANGA PEREZ BALBINA ISIDORA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -8707,14 +8707,14 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>MERCADO DE PUEBLO NUEVO PTO 46 ABARROTES</t>
+          <t>AAHH MICAELA BASTIDAS MZA. V LOTE. 10 Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>C001161027</t>
+          <t>C001159487</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>43760681</t>
+          <t>21867698</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>PINEDA RIVERA CHARO YESENIA</t>
+          <t>ESPINO LOZA OLIVIA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8759,14 +8759,14 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO PSTO. 89 Ica-Chincha-Pueblo Nuevo</t>
+          <t>ROSEDAL AV OSCAR R BENAVIDES Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>C001365658</t>
+          <t>C001517558</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>19953288</t>
+          <t>21843759</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>PAUCAR CRISOSTOMO ZENAIDA SEREGIA</t>
+          <t>DEL RIO DE MAZO DINA LUCILA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8811,14 +8811,14 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO Ica-Chincha-Pueblo Nuevo</t>
+          <t>AAHH JOSE CARLOS MARIATEGUI Ica-Chincha-Pueblo Nuevo</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>C004038222</t>
+          <t>C004024254</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>76232462</t>
+          <t>76050128</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>VILCAPUMA LAURA RUBY EDELYN</t>
+          <t>LEVANO QUISPE KARLA BRIGGITH</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8863,14 +8863,14 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>AV. VICTOR ANDRES BELAUNDE S/N</t>
+          <t>AA.HH SOL DE AURAHUA ICA-CHINCHA-PUEBLO NUEVO</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>C004059491</t>
+          <t>C004028231</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>21857339</t>
+          <t>75765350</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MATTA YEACHEE PABLO RUFINO</t>
+          <t>ROJAS CUSI ANA MARIA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8910,19 +8910,19 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>MERCADO DE PUEBLO NUEVO PTO 16 SEC. ABARROTE</t>
+          <t>UPIS SAN AGUSTIN ANTES DEL COLEGIO SAN AGUSTINPIS SAN AGUSTIN</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>C001476373</t>
+          <t>C004008584</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>21859308</t>
+          <t>70073142</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>CUBA FLORES JULIO CESAR</t>
+          <t>VILLANUEVA RAMOS MARIA ALEJANDRA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8962,19 +8962,19 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>AV. BELAUNDE 699 Ica-Chincha-Pueblo Nuevo</t>
+          <t>SAN AGUSTIN Mz F, Lot 15</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>C001522451</t>
+          <t>C004028216</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>21866718</t>
+          <t>76685293</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CARCAMO DE ROJAS DACIANA</t>
+          <t>SALAZAR CHINCHON ESTEFANI SOFIA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9014,19 +9014,19 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO Ica-Chincha-Pueblo Nuevo</t>
+          <t>UPIS SAN AGUSTIN ANTES DE LESDEMA POMA</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>C001498029</t>
+          <t>C001748703</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>45200917</t>
+          <t>21871626</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>CASTILLON HERRERA KLEYBER YONZON</t>
+          <t>GARCIA PAUCAR ANGELICA EDITH</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -9066,19 +9066,19 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>MERCADO PUEBLO NUEVO Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. UPIS SAN AGUSTIN / SAN LUIS MZA. D LOTE. 9 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>C001172358</t>
+          <t>C001730100</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>10218578158</t>
+          <t>10218877601</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>AURIS PAUCAR FELIPA FLORINDA</t>
+          <t>VALENZUELA LLANCARI SOLEDAD ROSARELA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -9118,19 +9118,19 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>AV. GROCIO PRADO NRO. 498 URB. AV GROCIO PRADO Ica-Chincha-Pueblo Nuevo</t>
+          <t>MZA. P LOTE. 10 URB. UPIS SAN AGUSTIN Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>C004238721</t>
+          <t>C004242601</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>72968601</t>
+          <t>73882979</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>GUILLEN DEL RIO YESENIA KARIN</t>
+          <t>MUNAYCO TORRES SARELA ISABEL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -9170,19 +9170,19 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Av. Artemio Molina 431</t>
+          <t>Av. Chavalina 379</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>C004202555</t>
+          <t>C004094513</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>45239970</t>
+          <t>21861197</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>ACUNA RUIZ JEFFERSON RUBEN</t>
+          <t>PEREZ TASAYCO MARTIN JULIO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9222,19 +9222,19 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Av. Grocio Prado 361</t>
+          <t>CALLE LUISA MASSARO 545 EL TIGRE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9249,22 +9249,22 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>C001376431</t>
+          <t>C001558100</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>20452591295</t>
+          <t>44284314</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>MI BRIAN E.I.R.L.</t>
+          <t>ALMEYDA DE LA CRUZ FREEDI JESUS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9274,19 +9274,19 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>AV. GROCIO PRADO NRO. 300 URB. AV GROCIO PRADO Ica-Chincha-Pueblo Nuevo</t>
+          <t>AV. PRIMAVERA 122 - Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>C004063324</t>
+          <t>C001718798</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>21871915</t>
+          <t>42645422</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>VILLAVICENCIO CARDENAS MARIA ROSANA</t>
+          <t>CARBAJAL MAGALLANES BLANCA ANKELLI</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9326,19 +9326,19 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Av. Grocio Prado nº 185 PUEBLO NUEVO</t>
+          <t>BARRIO EL TIGRE NRO. 143 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>C004061418</t>
+          <t>C004094490</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>45633006</t>
+          <t>72368070</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>MARCOS GALVEZ DIANA LIZETH</t>
+          <t>GUILLEN PACHAS KARINA LISSETT</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9378,19 +9378,19 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>AV. GROCIO PRADO 181 PUEBLO NUEVO</t>
+          <t>BARRIO EL TIGRE  391 CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>C001508434</t>
+          <t>C004069626</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>21844723</t>
+          <t>21794099</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>CAMPOS GARAY FLOR</t>
+          <t>CHOQUE ZAMBRANO ROSARIO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9430,19 +9430,19 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>JR. MIRAFLORES 319 Ica-Chincha-Pueblo Nuevo</t>
+          <t>SAN MATEO 115 EL TIGRE, CHINCHA ALTA</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>C001514817</t>
+          <t>C001518757</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9467,12 +9467,12 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>21864568</t>
+          <t>21800090</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>YOMONA DIAZ ROSARIO</t>
+          <t>TORRES SALVADOR CARMELA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>AV. PROGRESO 357 Ica-Chincha-Pueblo Nuevo</t>
+          <t>BARRIO EL TIGRE 235 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>C001529551</t>
+          <t>C001716446</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>21881934</t>
+          <t>42979079</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>CASTILLON CUEVA PEDRO ALBERTO</t>
+          <t>MAGALLANES TORRES CARMEN ROSA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -9534,19 +9534,19 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>AV UNION 117 Ica-Chincha-Pueblo Nuevo</t>
+          <t>BARRIO EL TIGRE 235 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>C001650653</t>
+          <t>C001652596</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>71282013</t>
+          <t>21863043</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>CANALES MADRID MELISA MILAGROS</t>
+          <t>SARAVIA CASAS ANITA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -9586,19 +9586,19 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>JR 23 DE MAYO 382 ESQUINA OVALO DE LA AMISTAD Ica-Chincha-Pueblo Nuevo</t>
+          <t>EL TIGRE 225 Ica-Chincha-Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9613,22 +9613,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>C004223454</t>
+          <t>C004013754</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>10218690594</t>
+          <t>15357653</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>YATACO FELIX EDDY</t>
+          <t>DE LA CRUZ ROMAN KARIM GABRIELA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -9638,19 +9638,19 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Calle Miraflores s/n</t>
+          <t>PROLONGACIÓN MAURO MINA 301 POR EL COLISEO</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>C004043542</t>
+          <t>C004177986</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>21856487</t>
+          <t>75485996</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>HERRERA GARAYAR DOMINGO WALDETRUDES</t>
+          <t>PACHAS HERNANDEZ MANUEL ARMANDO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -9690,19 +9690,19 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>AV. PROGRESO 269 ICA-CHINCHA-PUEBLO NUEVO</t>
+          <t>MERCADO CRUZ BLANCA S/N</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>C001531221</t>
+          <t>C000956382</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>21792612</t>
+          <t>21801006</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>CORNEJO JACOBO FRANCISCA FLORA</t>
+          <t>LOYOLA DE LEVANO MARIA ESTHER</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9747,14 +9747,14 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>CL. PEDRO RONCEROS 104 Ica-Chincha-Chincha Alta</t>
+          <t>MERCADO CRUZ BLANCA - Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>C001457211</t>
+          <t>C000956354</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>70075780</t>
+          <t>21859345</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>HERRERA FLORES GERALDINE MARIANELLY</t>
+          <t>AMPA MONDALGO ELSA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9794,19 +9794,19 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR 101 Ica-Chincha-Pueblo Nuevo</t>
+          <t>MERCADO CRUZ BLANCA - Chincha Alta</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-09-05 00:00:00</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>C001508435</t>
+          <t>C004036009</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9831,12 +9831,12 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>41703967</t>
+          <t>21824183</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>AGUIRRE SANTIAGO GABRIELA</t>
+          <t>HERRERA YANEZ ROXANA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Pueblo Nuevo (Chincha)</t>
+          <t>Chincha Alta (Chincha)</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>AV. ARTEMIO MOLINA 616 Ica-Chincha-Pueblo Nuevo</t>
+          <t>PASAJE MARTINEZ 101 CHINCHA ALTA</t>
         </is>
       </c>
     </row>
